--- a/zayavki/2026-10-29_Заявка_3.xlsx
+++ b/zayavki/2026-10-29_Заявка_3.xlsx
@@ -592,11 +592,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>17934</v>
+        <v>19728</v>
       </c>
       <c r="F4" s="4" t="n">
         <f aca="false">C4*E4</f>
-        <v>860832</v>
+        <v>946944</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -613,11 +613,11 @@
         <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9809</v>
+        <v>10789</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">C5*E5</f>
-        <v>588540</v>
+        <v>647340</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,11 +634,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5480</v>
+        <v>6028</v>
       </c>
       <c r="F6" s="4" t="n">
         <f aca="false">C6*E6</f>
-        <v>98640</v>
+        <v>108504</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -655,11 +655,11 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9478</v>
+        <v>10426</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">C7*E7</f>
-        <v>398076</v>
+        <v>437892</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -672,7 +672,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>10663</v>
+        <v>11729</v>
       </c>
       <c r="F8" s="5"/>
     </row>
@@ -690,11 +690,11 @@
         <v>12</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>61906</v>
+        <v>68096</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">C9*E9</f>
-        <v>1238120</v>
+        <v>1361920</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -711,11 +711,11 @@
         <v>12</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>31227</v>
+        <v>34350</v>
       </c>
       <c r="F10" s="4" t="n">
         <f aca="false">C10*E10</f>
-        <v>93681</v>
+        <v>103050</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -732,11 +732,11 @@
         <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>14686</v>
+        <v>16155</v>
       </c>
       <c r="F11" s="4" t="n">
         <f aca="false">C11*E11</f>
-        <v>102802</v>
+        <v>113085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -749,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>23840</v>
+        <v>26224</v>
       </c>
       <c r="F12" s="5"/>
     </row>
@@ -767,11 +767,11 @@
         <v>8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1076</v>
+        <v>1184</v>
       </c>
       <c r="F13" s="4" t="n">
         <f aca="false">C13*E13</f>
-        <v>322800</v>
+        <v>355200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -784,7 +784,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>947</v>
+        <v>1042</v>
       </c>
       <c r="F14" s="5"/>
     </row>
@@ -802,11 +802,11 @@
         <v>8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="F15" s="4" t="n">
         <f aca="false">C15*E15</f>
-        <v>38700</v>
+        <v>42570</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -823,11 +823,11 @@
         <v>8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>22800</v>
+        <v>25080</v>
       </c>
       <c r="F16" s="4" t="n">
         <f aca="false">C16*E16</f>
-        <v>547200</v>
+        <v>601920</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>11586</v>
+        <v>12745</v>
       </c>
       <c r="F17" s="5"/>
     </row>
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>28717</v>
+        <v>31588</v>
       </c>
       <c r="F20" s="3"/>
     </row>
@@ -906,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>35724</v>
+        <v>39296</v>
       </c>
       <c r="F21" s="5"/>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="F22" s="8" t="n">
         <f aca="false">F4+F5+F6+F7+F9+F10+F11+F13+F15+F16</f>
-        <v>4289391</v>
+        <v>4718425</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
